--- a/data/trans_dic/KIDM_C_3_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,57 +717,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,0; 10,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 19,56</t>
+          <t>3,64; 19,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 18,44</t>
+          <t>1,91; 18,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,87</t>
+          <t>0,0; 13,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 25,45</t>
+          <t>5,69; 24,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,72; 34,58</t>
+          <t>11,18; 34,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,83</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,02</t>
+          <t>0,86; 7,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 17,83</t>
+          <t>6,35; 18,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 23,47</t>
+          <t>8,86; 23,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,94</t>
+          <t>0,0; 15,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 33,44</t>
+          <t>10,4; 31,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 25,82</t>
+          <t>8,59; 26,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,14</t>
+          <t>0,0; 13,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,02</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 24,71</t>
+          <t>7,06; 27,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,77</t>
+          <t>1,22; 10,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>0,0; 14,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,82</t>
+          <t>0,0; 8,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,65; 25,27</t>
+          <t>10,46; 25,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 15,44</t>
+          <t>5,17; 15,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,84</t>
+          <t>0,0; 9,71</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,31</t>
+          <t>0,0; 16,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 27,29</t>
+          <t>9,0; 26,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,09</t>
+          <t>0,0; 10,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,54</t>
+          <t>0,0; 24,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,64</t>
+          <t>1,31; 10,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 23,43</t>
+          <t>4,36; 23,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 23,38</t>
+          <t>5,12; 21,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 9,25</t>
+          <t>1,66; 9,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 21,49</t>
+          <t>8,35; 21,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 15,21</t>
+          <t>3,82; 15,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,63</t>
+          <t>0,0; 8,62</t>
         </is>
       </c>
     </row>
@@ -1136,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 12,37</t>
+          <t>3,21; 11,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,8; 29,78</t>
+          <t>15,0; 30,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 12,52</t>
+          <t>3,87; 12,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 13,33</t>
+          <t>0,63; 12,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,16</t>
+          <t>0,98; 7,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,49</t>
+          <t>6,23; 16,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 12,86</t>
+          <t>3,56; 12,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,99</t>
+          <t>2,82; 8,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,78; 20,57</t>
+          <t>11,26; 20,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 10,59</t>
+          <t>4,31; 10,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,15</t>
+          <t>1,46; 8,29</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 13,94</t>
+          <t>2,51; 14,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 19,85</t>
+          <t>7,27; 19,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 16,14</t>
+          <t>4,77; 17,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 19,83</t>
+          <t>2,15; 21,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 13,15</t>
+          <t>2,97; 13,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 18,0</t>
+          <t>6,23; 18,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,87; 23,08</t>
+          <t>8,63; 22,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,55</t>
+          <t>0,0; 9,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,67</t>
+          <t>3,62; 11,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 17,1</t>
+          <t>7,67; 16,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 17,82</t>
+          <t>7,52; 17,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,44</t>
+          <t>1,58; 9,87</t>
         </is>
       </c>
     </row>
@@ -1416,42 +1417,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,31</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,22</t>
+          <t>0,0; 21,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,95; 21,01</t>
+          <t>1,91; 19,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 15,8</t>
+          <t>1,62; 14,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 13,12</t>
+          <t>1,76; 14,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 13,31</t>
+          <t>2,16; 12,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 13,59</t>
+          <t>2,83; 13,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,13</t>
+          <t>2,96; 7,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,43; 19,27</t>
+          <t>12,41; 19,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 11,46</t>
+          <t>6,38; 11,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,74</t>
+          <t>1,77; 6,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,94</t>
+          <t>2,21; 6,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 14,06</t>
+          <t>7,95; 13,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,72; 13,18</t>
+          <t>7,55; 13,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,91</t>
+          <t>0,69; 3,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,74</t>
+          <t>3,02; 5,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,12; 15,36</t>
+          <t>10,87; 15,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,61</t>
+          <t>7,59; 11,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,15</t>
+          <t>1,65; 4,34</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3492</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7972</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10554</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4090</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1342; 7065</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>621; 6029</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4603</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1947; 8546</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4195; 12825</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3258</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>643; 5473</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4520; 12972</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6208; 16474</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3264</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6209</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7543</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4935</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1894</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>11144</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>9437</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1744</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4012</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3390; 10408</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4229; 13079</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3926</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3747</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2432; 9489</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>582; 5129</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4729</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4790</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7015; 16781</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5013; 14976</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5980</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6897</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3480</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3401</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>10376</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5382</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4908</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3870; 11579</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2928</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3567</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>670; 5442</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1341; 7113</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2042; 8707</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1328; 7538</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6160; 16019</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2577; 10144</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3611</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5882</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18520</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8095</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10347</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6841</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8418</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>28868</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>14936</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5314</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2760; 10231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12691; 25381</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4315; 13814</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>421; 8678</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>796; 6143</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>6090; 16095</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3513; 12205</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6132</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4719; 13692</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>20535; 37220</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>9049; 22045</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2014; 11431</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3058</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9436</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6922</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2770</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4378</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7725</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10161</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1532</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7436</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17160</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1190; 6756</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5473; 14789</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3525; 12864</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>769; 7598</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1856; 8347</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4390; 12980</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6071; 16064</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5529</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3981; 12098</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>11181; 23782</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10856; 24535</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1516; 9441</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1178</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3566</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4608</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4081</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5105</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>636; 6530</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>571; 4977</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>656; 5402</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4106</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1271; 7366</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1993; 9607</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12994</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>46111</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>28307</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7930</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10918</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>33152</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>33693</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4786</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>23913</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>79263</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>62000</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>12716</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>7835; 19136</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>36712; 57061</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>20916; 38337</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3668; 14190</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6459; 17558</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>24073; 42331</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>25005; 43112</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1826; 10383</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>16825; 32757</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>65074; 92959</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>50028; 75631</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>7810; 20539</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_C_3_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,24</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 19,13</t>
+          <t>3,55; 19,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 18,54</t>
+          <t>2,01; 18,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,11</t>
+          <t>0,0; 13,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 24,99</t>
+          <t>7,18; 25,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 34,17</t>
+          <t>11,23; 34,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 9,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,29</t>
+          <t>0,85; 7,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 18,24</t>
+          <t>6,43; 19,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 23,52</t>
+          <t>8,29; 23,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,9</t>
+          <t>0,0; 14,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,4; 31,92</t>
+          <t>8,67; 31,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 26,56</t>
+          <t>8,12; 26,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,46</t>
+          <t>0,0; 13,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,72</t>
+          <t>0,0; 11,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 27,54</t>
+          <t>6,99; 25,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,75</t>
+          <t>1,22; 10,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,58</t>
+          <t>0,0; 14,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,76</t>
+          <t>0,0; 8,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,46; 25,02</t>
+          <t>10,41; 25,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 15,44</t>
+          <t>5,19; 15,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,71</t>
+          <t>0,0; 10,15</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,96</t>
+          <t>0,0; 14,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 26,94</t>
+          <t>7,84; 25,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,63</t>
+          <t>0,0; 11,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,52</t>
+          <t>0,0; 25,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 10,63</t>
+          <t>1,32; 10,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 23,11</t>
+          <t>4,18; 22,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 21,81</t>
+          <t>5,08; 22,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,41</t>
+          <t>1,68; 9,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,35; 21,72</t>
+          <t>8,4; 21,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 15,04</t>
+          <t>3,9; 15,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,62</t>
+          <t>0,0; 8,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,92</t>
+          <t>3,14; 12,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 30,01</t>
+          <t>15,1; 30,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 12,4</t>
+          <t>3,8; 11,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 12,92</t>
+          <t>0,36; 12,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,53</t>
+          <t>0,78; 8,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 16,47</t>
+          <t>6,22; 16,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 12,37</t>
+          <t>3,13; 13,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,66</t>
+          <t>0,0; 8,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,18</t>
+          <t>2,83; 8,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,26; 20,42</t>
+          <t>11,97; 20,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,49</t>
+          <t>4,31; 10,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,29</t>
+          <t>1,25; 7,72</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 14,26</t>
+          <t>2,52; 13,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 19,63</t>
+          <t>7,49; 21,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 17,39</t>
+          <t>4,81; 16,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 21,28</t>
+          <t>2,03; 18,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 13,34</t>
+          <t>3,02; 13,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 18,43</t>
+          <t>6,33; 18,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 22,85</t>
+          <t>8,43; 23,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,22</t>
+          <t>0,0; 9,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,0</t>
+          <t>3,84; 11,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 16,32</t>
+          <t>7,97; 16,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 17,01</t>
+          <t>8,12; 16,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 9,87</t>
+          <t>1,67; 9,63</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 11,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,72</t>
+          <t>0,0; 19,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,91; 19,57</t>
+          <t>1,87; 20,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,08</t>
+          <t>1,58; 14,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 14,54</t>
+          <t>1,78; 14,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,52</t>
+          <t>2,23; 13,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,83; 13,62</t>
+          <t>2,82; 13,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,22</t>
+          <t>3,16; 7,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,41; 19,28</t>
+          <t>12,12; 19,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,69</t>
+          <t>6,11; 11,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,85</t>
+          <t>1,72; 6,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,02</t>
+          <t>2,34; 5,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 13,97</t>
+          <t>8,33; 14,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 13,01</t>
+          <t>7,78; 13,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,91</t>
+          <t>0,67; 3,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,88</t>
+          <t>3,0; 5,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,87; 15,52</t>
+          <t>11,05; 15,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,47</t>
+          <t>7,61; 11,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,34</t>
+          <t>1,67; 4,21</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,17 +1927,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4090</t>
+          <t>0; 3595</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1342; 7065</t>
+          <t>1311; 7212</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>621; 6029</t>
+          <t>654; 6142</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1947,42 +1947,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4603</t>
+          <t>0; 4667</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1947; 8546</t>
+          <t>2455; 8800</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4195; 12825</t>
+          <t>4215; 12948</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3258</t>
+          <t>0; 3661</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>643; 5473</t>
+          <t>642; 5466</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4520; 12972</t>
+          <t>4577; 13855</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6208; 16474</t>
+          <t>5804; 16206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3264</t>
+          <t>0; 3204</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4012</t>
+          <t>0; 3677</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3390; 10408</t>
+          <t>2826; 10330</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4229; 13079</t>
+          <t>4001; 13134</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3926</t>
+          <t>0; 4048</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3747</t>
+          <t>0; 3399</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2432; 9489</t>
+          <t>2407; 8900</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>582; 5129</t>
+          <t>580; 5109</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4729</t>
+          <t>0; 4639</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4790</t>
+          <t>0; 4431</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7015; 16781</t>
+          <t>6979; 17283</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5013; 14976</t>
+          <t>5036; 15076</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 5980</t>
+          <t>0; 6253</t>
         </is>
       </c>
     </row>
@@ -2343,37 +2343,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4908</t>
+          <t>0; 4139</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3870; 11579</t>
+          <t>3368; 11064</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2928</t>
+          <t>0; 3145</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3567</t>
+          <t>0; 3671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>670; 5442</t>
+          <t>674; 5436</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1341; 7113</t>
+          <t>1286; 6977</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2042; 8707</t>
+          <t>2026; 9177</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,22 +2383,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1328; 7538</t>
+          <t>1348; 7641</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6160; 16019</t>
+          <t>6193; 15953</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2577; 10144</t>
+          <t>2632; 10689</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3611</t>
+          <t>0; 3670</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2760; 10231</t>
+          <t>2697; 10434</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12691; 25381</t>
+          <t>12769; 26089</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4315; 13814</t>
+          <t>4236; 13268</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>421; 8678</t>
+          <t>245; 8496</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>796; 6143</t>
+          <t>638; 6562</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6090; 16095</t>
+          <t>6075; 16120</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3513; 12205</t>
+          <t>3089; 13080</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6132</t>
+          <t>0; 5699</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4719; 13692</t>
+          <t>4731; 14222</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20535; 37220</t>
+          <t>21814; 37942</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9049; 22045</t>
+          <t>9050; 21759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2014; 11431</t>
+          <t>1720; 10645</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1190; 6756</t>
+          <t>1193; 6268</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5473; 14789</t>
+          <t>5642; 15822</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3525; 12864</t>
+          <t>3561; 12295</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>769; 7598</t>
+          <t>725; 6484</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1856; 8347</t>
+          <t>1892; 8605</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4390; 12980</t>
+          <t>4459; 12797</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6071; 16064</t>
+          <t>5925; 16198</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5529</t>
+          <t>0; 5521</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3981; 12098</t>
+          <t>4219; 12789</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11181; 23782</t>
+          <t>11613; 23851</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10856; 24535</t>
+          <t>11711; 23960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1516; 9441</t>
+          <t>1601; 9211</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4081</t>
+          <t>0; 4259</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5105</t>
+          <t>0; 4620</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>636; 6530</t>
+          <t>624; 6748</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>571; 4977</t>
+          <t>557; 5293</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>656; 5402</t>
+          <t>661; 5483</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3007,17 +3007,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4106</t>
+          <t>0; 4323</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1271; 7366</t>
+          <t>1313; 7926</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1993; 9607</t>
+          <t>1992; 9349</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7835; 19136</t>
+          <t>8386; 19478</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>36712; 57061</t>
+          <t>35853; 56448</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20916; 38337</t>
+          <t>20060; 37234</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3668; 14190</t>
+          <t>3571; 13928</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6459; 17558</t>
+          <t>6815; 17140</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24073; 42331</t>
+          <t>25226; 42684</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25005; 43112</t>
+          <t>25777; 45186</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1826; 10383</t>
+          <t>1784; 10482</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16825; 32757</t>
+          <t>16728; 31936</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65074; 92959</t>
+          <t>66178; 93446</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50028; 75631</t>
+          <t>50201; 76571</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7810; 20539</t>
+          <t>7899; 19903</t>
         </is>
       </c>
     </row>
